--- a/Storage/output_real_thermocline_2.xlsx
+++ b/Storage/output_real_thermocline_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,19 +436,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Q_loss_storage_PD</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Q_Storage_PD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>T_hot_storage_PD</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Q_loss_storage_PD</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Q_Storage_PD</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>T_cold_storage_PD</t>
@@ -482,6 +482,26 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mdot_bypass</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>m_dot_bypass_panda</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>volumen_bypass</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tnet_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>T_net_2</t>
         </is>
       </c>
     </row>
@@ -490,13 +510,13 @@
         <v>459515.4605233685</v>
       </c>
       <c r="B2" t="n">
+        <v>720.0000000000002</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D2" t="n">
         <v>354</v>
-      </c>
-      <c r="C2" t="n">
-        <v>720.0000000000002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>313</v>
@@ -516,6 +536,18 @@
       </c>
       <c r="K2" t="n">
         <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>359.7854751138729</v>
+      </c>
+      <c r="O2" t="n">
+        <v>359.7854751138729</v>
       </c>
     </row>
     <row r="3">
@@ -523,32 +555,48 @@
         <v>632368.0089951353</v>
       </c>
       <c r="B3" t="n">
+        <v>995.6973303627101</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-172796.4227983242</v>
+      </c>
+      <c r="D3" t="n">
         <v>363.4366509629564</v>
-      </c>
-      <c r="C3" t="n">
-        <v>994.7356293176007</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-172796.4227983242</v>
       </c>
       <c r="E3" t="n">
         <v>312.948175617675</v>
       </c>
       <c r="F3" t="n">
-        <v>5.262098493132912</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.737901506867088</v>
+        <v>8</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>to_Thot</t>
+        </is>
+      </c>
       <c r="J3" t="n">
         <v>0.88</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>359.8512518775687</v>
+      </c>
+      <c r="O3" t="n">
+        <v>359.8512518775687</v>
       </c>
     </row>
     <row r="4">
@@ -556,32 +604,48 @@
         <v>422634.2931833685</v>
       </c>
       <c r="B4" t="n">
+        <v>945.8955501090256</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36896.76946810613</v>
+      </c>
+      <c r="D4" t="n">
         <v>363.3165878899312</v>
       </c>
-      <c r="C4" t="n">
-        <v>944.8176431908136</v>
-      </c>
-      <c r="D4" t="n">
-        <v>36896.76946810613</v>
-      </c>
       <c r="E4" t="n">
-        <v>311.9570627575508</v>
+        <v>311.9545383075436</v>
       </c>
       <c r="F4" t="n">
-        <v>4.717874641438243</v>
+        <v>5.274797114465569</v>
       </c>
       <c r="G4" t="n">
-        <v>5.282125358561757</v>
+        <v>4.725202885534431</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J4" t="n">
         <v>0.15</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>304.7703260251605</v>
+      </c>
+      <c r="O4" t="n">
+        <v>304.7703260251605</v>
       </c>
     </row>
     <row r="5">
@@ -589,58 +653,74 @@
         <v>340305.6496531552</v>
       </c>
       <c r="B5" t="n">
+        <v>886.5888803210896</v>
+      </c>
+      <c r="C5" t="n">
+        <v>44219.21667357875</v>
+      </c>
+      <c r="D5" t="n">
         <v>363.1966918929459</v>
       </c>
-      <c r="C5" t="n">
-        <v>885.3864188014461</v>
-      </c>
-      <c r="D5" t="n">
-        <v>44219.21667357875</v>
-      </c>
       <c r="E5" t="n">
-        <v>311.0127825216964</v>
+        <v>311.0081570916847</v>
       </c>
       <c r="F5" t="n">
-        <v>4.065042076633019</v>
+        <v>4.732125222937468</v>
       </c>
       <c r="G5" t="n">
-        <v>5.934957923366981</v>
+        <v>5.267874777062532</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J5" t="n">
         <v>0.18</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>304.7249760799659</v>
+      </c>
+      <c r="O5" t="n">
+        <v>304.7249760799659</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>346992.8742741912</v>
+        <v>527079.5945278449</v>
       </c>
       <c r="B6" t="n">
+        <v>1119.025113966508</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-180031.3939303667</v>
+      </c>
+      <c r="D6" t="n">
         <v>363.0769627186374</v>
       </c>
-      <c r="C6" t="n">
-        <v>1124.00416563103</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0</v>
-      </c>
       <c r="E6" t="n">
-        <v>337.8984326102197</v>
+        <v>337.2700627148609</v>
       </c>
       <c r="F6" t="n">
-        <v>4.065042076633019</v>
+        <v>4.080928568728455</v>
       </c>
       <c r="G6" t="n">
-        <v>5.934957923366981</v>
+        <v>5.919071431271545</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -648,36 +728,48 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="K6" t="n">
-        <v>0.88</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>359.8206365948837</v>
+      </c>
+      <c r="O6" t="n">
+        <v>359.8206365948837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>309491.4496685705</v>
+        <v>380531.356196169</v>
       </c>
       <c r="B7" t="n">
+        <v>1210.545939943145</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-70869.43934414783</v>
+      </c>
+      <c r="D7" t="n">
         <v>362.957400114088</v>
       </c>
-      <c r="C7" t="n">
-        <v>1213.911629716595</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0</v>
-      </c>
       <c r="E7" t="n">
-        <v>348.0795218763728</v>
+        <v>347.6605118160756</v>
       </c>
       <c r="F7" t="n">
-        <v>4.065042076633019</v>
+        <v>4.080928568728455</v>
       </c>
       <c r="G7" t="n">
-        <v>5.934957923366981</v>
+        <v>5.919071431271545</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -685,36 +777,48 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K7" t="n">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>359.7954193397489</v>
+      </c>
+      <c r="O7" t="n">
+        <v>359.7954193397489</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>308250.5489549018</v>
+        <v>346693.8441418276</v>
       </c>
       <c r="B8" t="n">
+        <v>1259.344834831168</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-38205.21333113067</v>
+      </c>
+      <c r="D8" t="n">
         <v>362.8380037003711</v>
       </c>
-      <c r="C8" t="n">
-        <v>1260.971378913988</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0</v>
-      </c>
       <c r="E8" t="n">
-        <v>353.4474651690659</v>
+        <v>353.2390633188176</v>
       </c>
       <c r="F8" t="n">
-        <v>4.065042076633019</v>
+        <v>4.080928568728455</v>
       </c>
       <c r="G8" t="n">
-        <v>5.934957923366981</v>
+        <v>5.919071431271545</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -722,10 +826,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>359.7950299000894</v>
+      </c>
+      <c r="O8" t="n">
+        <v>359.7950299000894</v>
       </c>
     </row>
     <row r="9">
@@ -733,32 +849,48 @@
         <v>210816.5489239419</v>
       </c>
       <c r="B9" t="n">
+        <v>1102.622474812621</v>
+      </c>
+      <c r="C9" t="n">
+        <v>97474.60307585931</v>
+      </c>
+      <c r="D9" t="n">
         <v>362.7187729983778</v>
       </c>
-      <c r="C9" t="n">
-        <v>1103.0387824575</v>
-      </c>
-      <c r="D9" t="n">
-        <v>97474.60307585931</v>
-      </c>
       <c r="E9" t="n">
-        <v>341.1703882726404</v>
+        <v>340.9834515462841</v>
       </c>
       <c r="F9" t="n">
-        <v>2.582806381404594</v>
+        <v>4.080928568728455</v>
       </c>
       <c r="G9" t="n">
-        <v>7.417193618595406</v>
+        <v>5.919071431271545</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J9" t="n">
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>304.714848189956</v>
+      </c>
+      <c r="O9" t="n">
+        <v>304.714848189956</v>
       </c>
     </row>
     <row r="10">
@@ -766,58 +898,74 @@
         <v>186705.0862688652</v>
       </c>
       <c r="B10" t="n">
+        <v>917.6665589838047</v>
+      </c>
+      <c r="C10" t="n">
+        <v>121593.7160945785</v>
+      </c>
+      <c r="D10" t="n">
         <v>362.5997077585449</v>
       </c>
-      <c r="C10" t="n">
-        <v>916.7218105016344</v>
-      </c>
-      <c r="D10" t="n">
-        <v>121593.7160945785</v>
-      </c>
       <c r="E10" t="n">
-        <v>332.041910842931</v>
+        <v>331.8402488712323</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7437959386016098</v>
+        <v>2.633829664696566</v>
       </c>
       <c r="G10" t="n">
-        <v>9.256204061398391</v>
+        <v>7.366170335303434</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>304.7139625185237</v>
+      </c>
+      <c r="O10" t="n">
+        <v>304.7139625185237</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>233222.9945458027</v>
+        <v>321222.1950724465</v>
       </c>
       <c r="B11" t="n">
+        <v>1031.387582674604</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-87803.99835349538</v>
+      </c>
+      <c r="D11" t="n">
         <v>362.4808077317419</v>
       </c>
-      <c r="C11" t="n">
-        <v>1031.006953708289</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0</v>
-      </c>
       <c r="E11" t="n">
-        <v>340.2827115342475</v>
+        <v>340.1140084034037</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7437959386016098</v>
+        <v>0.8249565562853964</v>
       </c>
       <c r="G11" t="n">
-        <v>9.256204061398391</v>
+        <v>9.175043443714603</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -825,43 +973,120 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="K11" t="n">
-        <v>0.75</v>
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>359.7568800401515</v>
+      </c>
+      <c r="O11" t="n">
+        <v>359.7568800401515</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>171410.1833417491</v>
+        <v>329309.594508601</v>
       </c>
       <c r="B12" t="n">
+        <v>896.054828026942</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55213.88423492014</v>
+      </c>
+      <c r="D12" t="n">
         <v>362.362072669271</v>
       </c>
-      <c r="C12" t="n">
-        <v>996.9410101666036</v>
-      </c>
-      <c r="D12" t="n">
-        <v>24285.02733445958</v>
-      </c>
       <c r="E12" t="n">
-        <v>338.7754544494663</v>
+        <v>332.9369591100159</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3761792188146528</v>
+        <v>0.8249565562853964</v>
       </c>
       <c r="G12" t="n">
-        <v>9.623820781185348</v>
+        <v>9.175043443714603</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J12" t="n">
-        <v>0.1</v>
+        <v>0.2280270846776078</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.2719729153223922</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2719729153223922</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.983932544069427</v>
+      </c>
+      <c r="N12" t="n">
+        <v>304.7230219289451</v>
+      </c>
+      <c r="O12" t="n">
+        <v>304.7250704003923</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>195682.1531560196</v>
+      </c>
+      <c r="B13" t="n">
+        <v>816.9474423352418</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>362.243502322865</v>
+      </c>
+      <c r="E13" t="n">
+        <v>327.6631282419754</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.99999999995449e-06</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.99999</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.808780930239461</v>
+      </c>
+      <c r="N13" t="n">
+        <v>304.5459935351638</v>
+      </c>
+      <c r="O13" t="n">
+        <v>304.557445519701</v>
       </c>
     </row>
   </sheetData>

--- a/Storage/output_real_thermocline_2.xlsx
+++ b/Storage/output_real_thermocline_2.xlsx
@@ -510,16 +510,16 @@
         <v>459515.4605233685</v>
       </c>
       <c r="B2" t="n">
-        <v>720.0000000000002</v>
+        <v>719.0570204018327</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>354</v>
+        <v>353.8929709965774</v>
       </c>
       <c r="E2" t="n">
-        <v>313</v>
+        <v>312.948175617675</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -530,7 +530,11 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>discharge</t>
+        </is>
+      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -552,25 +556,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>632368.0089951353</v>
+        <v>632558.8811212903</v>
       </c>
       <c r="B3" t="n">
-        <v>995.6973303627101</v>
+        <v>995.8606626445105</v>
       </c>
       <c r="C3" t="n">
-        <v>-172796.4227983242</v>
+        <v>-172987.6145580661</v>
       </c>
       <c r="D3" t="n">
-        <v>363.4366509629564</v>
+        <v>363.5036573826133</v>
       </c>
       <c r="E3" t="n">
-        <v>312.948175617675</v>
+        <v>312.8964197275865</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5.274797114465569</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>4.725202885534431</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -601,25 +605,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>422634.2931833685</v>
+        <v>422592.2074891538</v>
       </c>
       <c r="B4" t="n">
-        <v>945.8955501090256</v>
+        <v>946.0093106112154</v>
       </c>
       <c r="C4" t="n">
-        <v>36896.76946810613</v>
+        <v>36939.17279510649</v>
       </c>
       <c r="D4" t="n">
-        <v>363.3165878899312</v>
+        <v>363.3835010564445</v>
       </c>
       <c r="E4" t="n">
-        <v>311.9545383075436</v>
+        <v>311.908827019605</v>
       </c>
       <c r="F4" t="n">
-        <v>5.274797114465569</v>
+        <v>4.7321252266781</v>
       </c>
       <c r="G4" t="n">
-        <v>4.725202885534431</v>
+        <v>5.2678747733219</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -642,33 +646,33 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>304.7703260251605</v>
+        <v>304.7703048552489</v>
       </c>
       <c r="O4" t="n">
-        <v>304.7703260251605</v>
+        <v>304.7703048552489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>340305.6496531552</v>
+        <v>340255.2762897755</v>
       </c>
       <c r="B5" t="n">
-        <v>886.5888803210896</v>
+        <v>886.6429843108282</v>
       </c>
       <c r="C5" t="n">
-        <v>44219.21667357875</v>
+        <v>44270.04034276029</v>
       </c>
       <c r="D5" t="n">
-        <v>363.1966918929459</v>
+        <v>363.2635119477564</v>
       </c>
       <c r="E5" t="n">
-        <v>311.0081570916847</v>
+        <v>310.9681813716248</v>
       </c>
       <c r="F5" t="n">
-        <v>4.732125222937468</v>
+        <v>4.080928580171215</v>
       </c>
       <c r="G5" t="n">
-        <v>5.267874777062532</v>
+        <v>5.919071419828785</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -691,33 +695,33 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>304.7249760799659</v>
+        <v>304.7249397540613</v>
       </c>
       <c r="O5" t="n">
-        <v>304.7249760799659</v>
+        <v>304.7249397540613</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>527079.5945278449</v>
+        <v>527226.7769591317</v>
       </c>
       <c r="B6" t="n">
-        <v>1119.025113966508</v>
+        <v>1119.267025000798</v>
       </c>
       <c r="C6" t="n">
-        <v>-180031.3939303667</v>
+        <v>-180178.8763336701</v>
       </c>
       <c r="D6" t="n">
-        <v>363.0769627186374</v>
+        <v>363.1436898029372</v>
       </c>
       <c r="E6" t="n">
-        <v>337.2700627148609</v>
+        <v>337.251303904575</v>
       </c>
       <c r="F6" t="n">
-        <v>4.080928568728455</v>
+        <v>4.080928580171215</v>
       </c>
       <c r="G6" t="n">
-        <v>5.919071431271545</v>
+        <v>5.919071419828785</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -748,25 +752,25 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>380531.356196169</v>
+        <v>380590.1800679831</v>
       </c>
       <c r="B7" t="n">
-        <v>1210.545939943145</v>
+        <v>1210.864013805341</v>
       </c>
       <c r="C7" t="n">
-        <v>-70869.43934414783</v>
+        <v>-70928.37756848137</v>
       </c>
       <c r="D7" t="n">
-        <v>362.957400114088</v>
+        <v>363.024034368821</v>
       </c>
       <c r="E7" t="n">
-        <v>347.6605118160756</v>
+        <v>347.6503952684138</v>
       </c>
       <c r="F7" t="n">
-        <v>4.080928568728455</v>
+        <v>4.080928580171215</v>
       </c>
       <c r="G7" t="n">
-        <v>5.919071431271545</v>
+        <v>5.919071419828785</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -797,25 +801,25 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>346693.8441418276</v>
+        <v>346725.5937971388</v>
       </c>
       <c r="B8" t="n">
-        <v>1259.344834831168</v>
+        <v>1259.704178805812</v>
       </c>
       <c r="C8" t="n">
-        <v>-38205.21333113067</v>
+        <v>-38237.03414825977</v>
       </c>
       <c r="D8" t="n">
-        <v>362.8380037003711</v>
+        <v>362.9045453926869</v>
       </c>
       <c r="E8" t="n">
-        <v>353.2390633188176</v>
+        <v>353.2336588640051</v>
       </c>
       <c r="F8" t="n">
-        <v>4.080928568728455</v>
+        <v>4.080928580171215</v>
       </c>
       <c r="G8" t="n">
-        <v>5.919071431271545</v>
+        <v>5.919071419828785</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -846,25 +850,25 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>210816.5489239419</v>
+        <v>210705.1544153224</v>
       </c>
       <c r="B9" t="n">
-        <v>1102.622474812621</v>
+        <v>1102.84050417266</v>
       </c>
       <c r="C9" t="n">
-        <v>97474.60307585931</v>
+        <v>97587.02221508163</v>
       </c>
       <c r="D9" t="n">
-        <v>362.7187729983778</v>
+        <v>362.7852223390952</v>
       </c>
       <c r="E9" t="n">
-        <v>340.9834515462841</v>
+        <v>340.9794243974138</v>
       </c>
       <c r="F9" t="n">
-        <v>4.080928568728455</v>
+        <v>2.633829725526953</v>
       </c>
       <c r="G9" t="n">
-        <v>5.919071431271545</v>
+        <v>7.366170274473047</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -887,33 +891,33 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>304.714848189956</v>
+        <v>304.7147433711469</v>
       </c>
       <c r="O9" t="n">
-        <v>304.714848189956</v>
+        <v>304.7147433711469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>186705.0862688652</v>
+        <v>186565.985414873</v>
       </c>
       <c r="B10" t="n">
-        <v>917.6665589838047</v>
+        <v>917.7069963790077</v>
       </c>
       <c r="C10" t="n">
-        <v>121593.7160945785</v>
+        <v>121734.0982663125</v>
       </c>
       <c r="D10" t="n">
-        <v>362.5997077585449</v>
+        <v>362.6660648867391</v>
       </c>
       <c r="E10" t="n">
-        <v>331.8402488712323</v>
+        <v>331.8372202479246</v>
       </c>
       <c r="F10" t="n">
-        <v>2.633829664696566</v>
+        <v>0.8249566946600939</v>
       </c>
       <c r="G10" t="n">
-        <v>7.366170335303434</v>
+        <v>9.175043305339907</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -936,33 +940,33 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>304.7139625185237</v>
+        <v>304.7138308562813</v>
       </c>
       <c r="O10" t="n">
-        <v>304.7139625185237</v>
+        <v>304.7138308562813</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>321222.1950724465</v>
+        <v>321231.6841598594</v>
       </c>
       <c r="B11" t="n">
-        <v>1031.387582674604</v>
+        <v>1031.440254119644</v>
       </c>
       <c r="C11" t="n">
-        <v>-87803.99835349538</v>
+        <v>-87813.51263035301</v>
       </c>
       <c r="D11" t="n">
-        <v>362.4808077317419</v>
+        <v>362.547072786247</v>
       </c>
       <c r="E11" t="n">
-        <v>340.1140084034037</v>
+        <v>340.1118771220581</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8249565562853964</v>
+        <v>0.8249566946600939</v>
       </c>
       <c r="G11" t="n">
-        <v>9.175043443714603</v>
+        <v>9.175043305339907</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -993,25 +997,25 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>329309.594508601</v>
+        <v>329246.3832528718</v>
       </c>
       <c r="B12" t="n">
-        <v>896.054828026942</v>
+        <v>953.8659769236274</v>
       </c>
       <c r="C12" t="n">
-        <v>55213.88423492014</v>
+        <v>55277.65454069523</v>
       </c>
       <c r="D12" t="n">
-        <v>362.362072669271</v>
+        <v>362.4282457886799</v>
       </c>
       <c r="E12" t="n">
-        <v>332.9369591100159</v>
+        <v>336.7910394910355</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8249565562853964</v>
+        <v>9.99999999995449e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>9.175043443714603</v>
+        <v>9.99999</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1022,22 +1026,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.2280270846776078</v>
+        <v>0.2280271304519265</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2719729153223922</v>
+        <v>0.2719728695480734</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2719729153223922</v>
+        <v>0.2719728695480734</v>
       </c>
       <c r="M12" t="n">
-        <v>0.983932544069427</v>
+        <v>0.9839323638795355</v>
       </c>
       <c r="N12" t="n">
-        <v>304.7230219289451</v>
+        <v>304.7229205680048</v>
       </c>
       <c r="O12" t="n">
-        <v>304.7250704003923</v>
+        <v>304.7250248606335</v>
       </c>
     </row>
     <row r="13">
@@ -1045,16 +1049,16 @@
         <v>195682.1531560196</v>
       </c>
       <c r="B13" t="n">
-        <v>816.9474423352418</v>
+        <v>952.612197171146</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>362.243502322865</v>
+        <v>362.3095836455308</v>
       </c>
       <c r="E13" t="n">
-        <v>327.6631282419754</v>
+        <v>336.7074542092803</v>
       </c>
       <c r="F13" t="n">
         <v>9.99999999995449e-06</v>
@@ -1083,7 +1087,7 @@
         <v>1.808780930239461</v>
       </c>
       <c r="N13" t="n">
-        <v>304.5459935351638</v>
+        <v>304.5456647229985</v>
       </c>
       <c r="O13" t="n">
         <v>304.557445519701</v>
